--- a/RESULTS/tables/survival_km_curve_external_by_risk_group.xlsx
+++ b/RESULTS/tables/survival_km_curve_external_by_risk_group.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E372"/>
+  <dimension ref="A1:E371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,13 +498,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9975868725868725</v>
+        <v>0.9985521235521234</v>
       </c>
       <c r="C4" t="n">
         <v>2070</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -514,16 +514,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9966216216216215</v>
+        <v>0.998069498069498</v>
       </c>
       <c r="C5" t="n">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -533,13 +533,13 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>0.996138996138996</v>
+        <v>0.9975868725868725</v>
       </c>
       <c r="C6" t="n">
-        <v>2065</v>
+        <v>2068</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -552,13 +552,13 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9956563706563706</v>
+        <v>0.9971042471042471</v>
       </c>
       <c r="C7" t="n">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -571,13 +571,13 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9951737451737451</v>
+        <v>0.9966216216216216</v>
       </c>
       <c r="C8" t="n">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -590,13 +590,13 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9946911196911197</v>
+        <v>0.9961389961389961</v>
       </c>
       <c r="C9" t="n">
-        <v>2062</v>
+        <v>2065</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -609,16 +609,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9937258687258688</v>
+        <v>0.9956563706563707</v>
       </c>
       <c r="C10" t="n">
-        <v>2061</v>
+        <v>2064</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -631,10 +631,10 @@
         <v>31</v>
       </c>
       <c r="B11" t="n">
-        <v>0.9932432432432432</v>
+        <v>0.9951737451737452</v>
       </c>
       <c r="C11" t="n">
-        <v>2059</v>
+        <v>2063</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -647,13 +647,13 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" t="n">
-        <v>0.9927606177606177</v>
+        <v>0.9946911196911198</v>
       </c>
       <c r="C12" t="n">
-        <v>2058</v>
+        <v>2062</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -666,16 +666,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B13" t="n">
-        <v>0.9922779922779923</v>
+        <v>0.9937258687258689</v>
       </c>
       <c r="C13" t="n">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -685,13 +685,13 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B14" t="n">
-        <v>0.9917953667953668</v>
+        <v>0.9932432432432433</v>
       </c>
       <c r="C14" t="n">
-        <v>2056</v>
+        <v>2059</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -704,13 +704,13 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B15" t="n">
-        <v>0.9913127413127414</v>
+        <v>0.9927606177606179</v>
       </c>
       <c r="C15" t="n">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -723,13 +723,13 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B16" t="n">
-        <v>0.9908301158301159</v>
+        <v>0.9922779922779924</v>
       </c>
       <c r="C16" t="n">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -745,13 +745,13 @@
         <v>61</v>
       </c>
       <c r="B17" t="n">
-        <v>0.988899613899614</v>
+        <v>0.991795366795367</v>
       </c>
       <c r="C17" t="n">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>62</v>
       </c>
       <c r="B18" t="n">
-        <v>0.9884169884169886</v>
+        <v>0.9913127413127415</v>
       </c>
       <c r="C18" t="n">
-        <v>2049</v>
+        <v>2055</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B19" t="n">
-        <v>0.9879343629343631</v>
+        <v>0.990830115830116</v>
       </c>
       <c r="C19" t="n">
-        <v>2048</v>
+        <v>2054</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -799,13 +799,13 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9874517374517376</v>
+        <v>0.9903474903474906</v>
       </c>
       <c r="C20" t="n">
-        <v>2047</v>
+        <v>2053</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -818,13 +818,13 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9869691119691122</v>
+        <v>0.9898648648648651</v>
       </c>
       <c r="C21" t="n">
-        <v>2046</v>
+        <v>2052</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -837,13 +837,13 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B22" t="n">
-        <v>0.9864864864864867</v>
+        <v>0.9893822393822397</v>
       </c>
       <c r="C22" t="n">
-        <v>2045</v>
+        <v>2051</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -856,13 +856,13 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9860038610038613</v>
+        <v>0.9888996138996142</v>
       </c>
       <c r="C23" t="n">
-        <v>2044</v>
+        <v>2050</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -875,13 +875,13 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B24" t="n">
-        <v>0.9855212355212357</v>
+        <v>0.9884169884169888</v>
       </c>
       <c r="C24" t="n">
-        <v>2043</v>
+        <v>2049</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
@@ -894,13 +894,13 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B25" t="n">
-        <v>0.9850386100386103</v>
+        <v>0.9879343629343633</v>
       </c>
       <c r="C25" t="n">
-        <v>2042</v>
+        <v>2048</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
@@ -913,13 +913,13 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B26" t="n">
-        <v>0.9845559845559848</v>
+        <v>0.9874517374517379</v>
       </c>
       <c r="C26" t="n">
-        <v>2041</v>
+        <v>2047</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -932,16 +932,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B27" t="n">
-        <v>0.9840733590733594</v>
+        <v>0.9864864864864868</v>
       </c>
       <c r="C27" t="n">
-        <v>2040</v>
+        <v>2046</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -951,13 +951,13 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B28" t="n">
-        <v>0.9835907335907339</v>
+        <v>0.9860038610038614</v>
       </c>
       <c r="C28" t="n">
-        <v>2039</v>
+        <v>2044</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
@@ -970,16 +970,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B29" t="n">
-        <v>0.9831081081081084</v>
+        <v>0.9850386100386105</v>
       </c>
       <c r="C29" t="n">
-        <v>2038</v>
+        <v>2043</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -989,16 +989,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B30" t="n">
-        <v>0.9821428571428575</v>
+        <v>0.984555984555985</v>
       </c>
       <c r="C30" t="n">
-        <v>2037</v>
+        <v>2041</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1008,13 +1008,13 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B31" t="n">
-        <v>0.9816602316602321</v>
+        <v>0.9840733590733596</v>
       </c>
       <c r="C31" t="n">
-        <v>2035</v>
+        <v>2040</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
@@ -1027,16 +1027,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B32" t="n">
-        <v>0.9811776061776066</v>
+        <v>0.9831081081081086</v>
       </c>
       <c r="C32" t="n">
-        <v>2034</v>
+        <v>2039</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1046,13 +1046,13 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B33" t="n">
-        <v>0.9806949806949811</v>
+        <v>0.9826254826254831</v>
       </c>
       <c r="C33" t="n">
-        <v>2033</v>
+        <v>2037</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
@@ -1065,13 +1065,13 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B34" t="n">
-        <v>0.9802123552123556</v>
+        <v>0.9821428571428575</v>
       </c>
       <c r="C34" t="n">
-        <v>2032</v>
+        <v>2036</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
@@ -1087,13 +1087,13 @@
         <v>121</v>
       </c>
       <c r="B35" t="n">
-        <v>0.9797297297297302</v>
+        <v>0.9811776061776065</v>
       </c>
       <c r="C35" t="n">
-        <v>2031</v>
+        <v>2035</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1106,10 +1106,10 @@
         <v>125</v>
       </c>
       <c r="B36" t="n">
-        <v>0.9787644787644793</v>
+        <v>0.9802123552123556</v>
       </c>
       <c r="C36" t="n">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
@@ -1122,13 +1122,13 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B37" t="n">
-        <v>0.9782818532818538</v>
+        <v>0.9797297297297302</v>
       </c>
       <c r="C37" t="n">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
@@ -1144,10 +1144,10 @@
         <v>131</v>
       </c>
       <c r="B38" t="n">
-        <v>0.9777992277992283</v>
+        <v>0.9792471042471046</v>
       </c>
       <c r="C38" t="n">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
@@ -1160,13 +1160,13 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B39" t="n">
-        <v>0.9773166023166029</v>
+        <v>0.9787644787644791</v>
       </c>
       <c r="C39" t="n">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
@@ -1179,13 +1179,13 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B40" t="n">
-        <v>0.9768339768339774</v>
+        <v>0.9782818532818537</v>
       </c>
       <c r="C40" t="n">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D40" t="n">
         <v>1</v>
@@ -1198,13 +1198,13 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="B41" t="n">
-        <v>0.9763513513513519</v>
+        <v>0.9777992277992282</v>
       </c>
       <c r="C41" t="n">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
@@ -1217,13 +1217,13 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="B42" t="n">
-        <v>0.9758687258687264</v>
+        <v>0.9773166023166028</v>
       </c>
       <c r="C42" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
@@ -1236,13 +1236,13 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B43" t="n">
-        <v>0.975386100386101</v>
+        <v>0.9768339768339773</v>
       </c>
       <c r="C43" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
@@ -1255,13 +1255,13 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B44" t="n">
-        <v>0.9749034749034755</v>
+        <v>0.9763513513513518</v>
       </c>
       <c r="C44" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D44" t="n">
         <v>1</v>
@@ -1274,13 +1274,13 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B45" t="n">
-        <v>0.9744208494208501</v>
+        <v>0.9758687258687263</v>
       </c>
       <c r="C45" t="n">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
@@ -1293,35 +1293,35 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>0.9753861003861009</v>
       </c>
       <c r="C46" t="n">
-        <v>2072</v>
+        <v>2022</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Medium predicted risk</t>
+          <t>Low predicted risk</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="B47" t="n">
-        <v>0.9980694980694981</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
         <v>2072</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="B48" t="n">
-        <v>0.9971042471042472</v>
+        <v>0.9971042471042471</v>
       </c>
       <c r="C48" t="n">
-        <v>2068</v>
+        <v>2072</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1350,16 +1350,16 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B49" t="n">
-        <v>0.9966216216216217</v>
+        <v>0.996138996138996</v>
       </c>
       <c r="C49" t="n">
         <v>2066</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1369,16 +1369,16 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B50" t="n">
-        <v>0.9961389961389963</v>
+        <v>0.9946911196911196</v>
       </c>
       <c r="C50" t="n">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1388,16 +1388,16 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B51" t="n">
-        <v>0.9937258687258689</v>
+        <v>0.9942084942084941</v>
       </c>
       <c r="C51" t="n">
-        <v>2064</v>
+        <v>2061</v>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1407,13 +1407,13 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B52" t="n">
-        <v>0.992760617760618</v>
+        <v>0.9932432432432431</v>
       </c>
       <c r="C52" t="n">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="D52" t="n">
         <v>2</v>
@@ -1426,16 +1426,16 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B53" t="n">
-        <v>0.9917953667953671</v>
+        <v>0.9927606177606176</v>
       </c>
       <c r="C53" t="n">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1445,13 +1445,13 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B54" t="n">
-        <v>0.9913127413127416</v>
+        <v>0.9922779922779922</v>
       </c>
       <c r="C54" t="n">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
@@ -1464,13 +1464,13 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B55" t="n">
-        <v>0.9908301158301162</v>
+        <v>0.9917953667953667</v>
       </c>
       <c r="C55" t="n">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
@@ -1483,13 +1483,13 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56" t="n">
-        <v>0.9893822393822397</v>
+        <v>0.9903474903474903</v>
       </c>
       <c r="C56" t="n">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="D56" t="n">
         <v>3</v>
@@ -1502,13 +1502,13 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B57" t="n">
-        <v>0.9888996138996142</v>
+        <v>0.9898648648648648</v>
       </c>
       <c r="C57" t="n">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
@@ -1524,10 +1524,10 @@
         <v>14</v>
       </c>
       <c r="B58" t="n">
-        <v>0.9879343629343633</v>
+        <v>0.9888996138996139</v>
       </c>
       <c r="C58" t="n">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
@@ -1543,13 +1543,13 @@
         <v>15</v>
       </c>
       <c r="B59" t="n">
-        <v>0.9864864864864868</v>
+        <v>0.987934362934363</v>
       </c>
       <c r="C59" t="n">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B60" t="n">
-        <v>0.9855212355212359</v>
+        <v>0.9874517374517375</v>
       </c>
       <c r="C60" t="n">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1578,16 +1578,16 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B61" t="n">
-        <v>0.983590733590734</v>
+        <v>0.9860038610038611</v>
       </c>
       <c r="C61" t="n">
-        <v>2042</v>
+        <v>2046</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1597,16 +1597,16 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B62" t="n">
-        <v>0.9821428571428575</v>
+        <v>0.9855212355212355</v>
       </c>
       <c r="C62" t="n">
-        <v>2038</v>
+        <v>2043</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1616,16 +1616,16 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B63" t="n">
-        <v>0.9806949806949811</v>
+        <v>0.9845559845559845</v>
       </c>
       <c r="C63" t="n">
-        <v>2035</v>
+        <v>2042</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1635,16 +1635,16 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B64" t="n">
-        <v>0.9802123552123556</v>
+        <v>0.983108108108108</v>
       </c>
       <c r="C64" t="n">
-        <v>2032</v>
+        <v>2040</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B65" t="n">
-        <v>0.9792471042471047</v>
+        <v>0.9816602316602315</v>
       </c>
       <c r="C65" t="n">
-        <v>2031</v>
+        <v>2037</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1673,16 +1673,16 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B66" t="n">
-        <v>0.9777992277992282</v>
+        <v>0.9811776061776061</v>
       </c>
       <c r="C66" t="n">
-        <v>2029</v>
+        <v>2034</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1692,16 +1692,16 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B67" t="n">
-        <v>0.9768339768339772</v>
+        <v>0.9797297297297296</v>
       </c>
       <c r="C67" t="n">
-        <v>2026</v>
+        <v>2033</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1711,16 +1711,16 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B68" t="n">
-        <v>0.9758687258687263</v>
+        <v>0.979247104247104</v>
       </c>
       <c r="C68" t="n">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -1730,16 +1730,16 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B69" t="n">
-        <v>0.9753861003861009</v>
+        <v>0.978281853281853</v>
       </c>
       <c r="C69" t="n">
-        <v>2022</v>
+        <v>2029</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -1749,13 +1749,13 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B70" t="n">
-        <v>0.9749034749034754</v>
+        <v>0.9777992277992276</v>
       </c>
       <c r="C70" t="n">
-        <v>2021</v>
+        <v>2027</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
@@ -1768,16 +1768,16 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B71" t="n">
-        <v>0.9729729729729735</v>
+        <v>0.9773166023166021</v>
       </c>
       <c r="C71" t="n">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -1787,16 +1787,16 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B72" t="n">
-        <v>0.972490347490348</v>
+        <v>0.9763513513513511</v>
       </c>
       <c r="C72" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -1806,16 +1806,16 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B73" t="n">
-        <v>0.9710424710424715</v>
+        <v>0.9753861003861002</v>
       </c>
       <c r="C73" t="n">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -1825,13 +1825,13 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B74" t="n">
-        <v>0.9700772200772206</v>
+        <v>0.9744208494208493</v>
       </c>
       <c r="C74" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="D74" t="n">
         <v>2</v>
@@ -1844,16 +1844,16 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B75" t="n">
-        <v>0.9681467181467187</v>
+        <v>0.9739382239382238</v>
       </c>
       <c r="C75" t="n">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="D75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -1863,13 +1863,13 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B76" t="n">
-        <v>0.9676640926640931</v>
+        <v>0.9734555984555984</v>
       </c>
       <c r="C76" t="n">
-        <v>2006</v>
+        <v>2018</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
@@ -1882,16 +1882,16 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B77" t="n">
-        <v>0.9657335907335912</v>
+        <v>0.9729729729729728</v>
       </c>
       <c r="C77" t="n">
-        <v>2005</v>
+        <v>2017</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -1901,13 +1901,13 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B78" t="n">
-        <v>0.9647683397683403</v>
+        <v>0.9720077220077219</v>
       </c>
       <c r="C78" t="n">
-        <v>2001</v>
+        <v>2016</v>
       </c>
       <c r="D78" t="n">
         <v>2</v>
@@ -1920,16 +1920,16 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B79" t="n">
-        <v>0.9638030888030893</v>
+        <v>0.9715250965250964</v>
       </c>
       <c r="C79" t="n">
-        <v>1999</v>
+        <v>2014</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -1939,16 +1939,16 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B80" t="n">
-        <v>0.9623552123552128</v>
+        <v>0.9705598455598455</v>
       </c>
       <c r="C80" t="n">
-        <v>1997</v>
+        <v>2013</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -1958,16 +1958,16 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B81" t="n">
-        <v>0.9599420849420853</v>
+        <v>0.9691119691119692</v>
       </c>
       <c r="C81" t="n">
-        <v>1994</v>
+        <v>2011</v>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -1977,16 +1977,16 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B82" t="n">
-        <v>0.9594594594594599</v>
+        <v>0.9671814671814672</v>
       </c>
       <c r="C82" t="n">
-        <v>1989</v>
+        <v>2008</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -1996,16 +1996,16 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B83" t="n">
-        <v>0.9589768339768343</v>
+        <v>0.9662162162162162</v>
       </c>
       <c r="C83" t="n">
-        <v>1988</v>
+        <v>2004</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2015,16 +2015,16 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B84" t="n">
-        <v>0.9570463320463324</v>
+        <v>0.9652509652509653</v>
       </c>
       <c r="C84" t="n">
-        <v>1987</v>
+        <v>2002</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B85" t="n">
-        <v>0.9560810810810814</v>
+        <v>0.9623552123552124</v>
       </c>
       <c r="C85" t="n">
-        <v>1983</v>
+        <v>2000</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2053,16 +2053,16 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B86" t="n">
-        <v>0.9555984555984558</v>
+        <v>0.9613899613899614</v>
       </c>
       <c r="C86" t="n">
-        <v>1981</v>
+        <v>1994</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2072,16 +2072,16 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B87" t="n">
-        <v>0.9541505791505794</v>
+        <v>0.9609073359073359</v>
       </c>
       <c r="C87" t="n">
-        <v>1980</v>
+        <v>1992</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2091,16 +2091,16 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B88" t="n">
-        <v>0.9531853281853285</v>
+        <v>0.9594594594594594</v>
       </c>
       <c r="C88" t="n">
-        <v>1977</v>
+        <v>1991</v>
       </c>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2110,16 +2110,16 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B89" t="n">
-        <v>0.9517374517374521</v>
+        <v>0.9584942084942085</v>
       </c>
       <c r="C89" t="n">
-        <v>1975</v>
+        <v>1988</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2129,16 +2129,16 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B90" t="n">
-        <v>0.9512548262548266</v>
+        <v>0.957046332046332</v>
       </c>
       <c r="C90" t="n">
-        <v>1972</v>
+        <v>1986</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2148,16 +2148,16 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B91" t="n">
-        <v>0.9507722007722011</v>
+        <v>0.956081081081081</v>
       </c>
       <c r="C91" t="n">
-        <v>1971</v>
+        <v>1983</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2167,16 +2167,16 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B92" t="n">
-        <v>0.9488416988416992</v>
+        <v>0.9551158301158301</v>
       </c>
       <c r="C92" t="n">
-        <v>1970</v>
+        <v>1981</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -2186,16 +2186,16 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B93" t="n">
-        <v>0.9478764478764482</v>
+        <v>0.9536679536679536</v>
       </c>
       <c r="C93" t="n">
-        <v>1966</v>
+        <v>1979</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2205,16 +2205,16 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B94" t="n">
-        <v>0.9459459459459463</v>
+        <v>0.9527027027027026</v>
       </c>
       <c r="C94" t="n">
-        <v>1964</v>
+        <v>1976</v>
       </c>
       <c r="D94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2224,16 +2224,16 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B95" t="n">
-        <v>0.9449806949806953</v>
+        <v>0.9512548262548262</v>
       </c>
       <c r="C95" t="n">
-        <v>1960</v>
+        <v>1974</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2243,16 +2243,16 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B96" t="n">
-        <v>0.9425675675675678</v>
+        <v>0.9507722007722007</v>
       </c>
       <c r="C96" t="n">
-        <v>1958</v>
+        <v>1971</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2262,13 +2262,13 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B97" t="n">
-        <v>0.9416023166023169</v>
+        <v>0.9498069498069498</v>
       </c>
       <c r="C97" t="n">
-        <v>1953</v>
+        <v>1970</v>
       </c>
       <c r="D97" t="n">
         <v>2</v>
@@ -2281,16 +2281,16 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B98" t="n">
-        <v>0.9401544401544404</v>
+        <v>0.9478764478764479</v>
       </c>
       <c r="C98" t="n">
-        <v>1951</v>
+        <v>1968</v>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2300,16 +2300,16 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B99" t="n">
-        <v>0.9377413127413129</v>
+        <v>0.9459459459459459</v>
       </c>
       <c r="C99" t="n">
-        <v>1948</v>
+        <v>1964</v>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2319,16 +2319,16 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B100" t="n">
-        <v>0.9362934362934364</v>
+        <v>0.9425675675675675</v>
       </c>
       <c r="C100" t="n">
-        <v>1943</v>
+        <v>1960</v>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -2338,16 +2338,16 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B101" t="n">
-        <v>0.9353281853281855</v>
+        <v>0.9420849420849421</v>
       </c>
       <c r="C101" t="n">
-        <v>1940</v>
+        <v>1953</v>
       </c>
       <c r="D101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -2360,10 +2360,10 @@
         <v>64</v>
       </c>
       <c r="B102" t="n">
-        <v>0.9348455598455601</v>
+        <v>0.9416023166023165</v>
       </c>
       <c r="C102" t="n">
-        <v>1938</v>
+        <v>1952</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -2379,13 +2379,13 @@
         <v>65</v>
       </c>
       <c r="B103" t="n">
-        <v>0.9338803088803092</v>
+        <v>0.9401544401544401</v>
       </c>
       <c r="C103" t="n">
-        <v>1937</v>
+        <v>1951</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2398,13 +2398,13 @@
         <v>66</v>
       </c>
       <c r="B104" t="n">
-        <v>0.9329150579150581</v>
+        <v>0.9396718146718145</v>
       </c>
       <c r="C104" t="n">
-        <v>1935</v>
+        <v>1948</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2417,13 +2417,13 @@
         <v>67</v>
       </c>
       <c r="B105" t="n">
-        <v>0.9314671814671817</v>
+        <v>0.9387065637065636</v>
       </c>
       <c r="C105" t="n">
-        <v>1933</v>
+        <v>1947</v>
       </c>
       <c r="D105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         <v>68</v>
       </c>
       <c r="B106" t="n">
-        <v>0.9295366795366797</v>
+        <v>0.9367760617760617</v>
       </c>
       <c r="C106" t="n">
-        <v>1930</v>
+        <v>1945</v>
       </c>
       <c r="D106" t="n">
         <v>4</v>
@@ -2455,13 +2455,13 @@
         <v>69</v>
       </c>
       <c r="B107" t="n">
-        <v>0.9280888030888034</v>
+        <v>0.9358108108108107</v>
       </c>
       <c r="C107" t="n">
-        <v>1926</v>
+        <v>1941</v>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2471,16 +2471,16 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B108" t="n">
-        <v>0.9276061776061779</v>
+        <v>0.9348455598455598</v>
       </c>
       <c r="C108" t="n">
-        <v>1923</v>
+        <v>1939</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2490,16 +2490,16 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B109" t="n">
-        <v>0.9266409266409269</v>
+        <v>0.9333976833976834</v>
       </c>
       <c r="C109" t="n">
-        <v>1922</v>
+        <v>1937</v>
       </c>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2509,16 +2509,16 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B110" t="n">
-        <v>0.9251930501930504</v>
+        <v>0.9329150579150579</v>
       </c>
       <c r="C110" t="n">
-        <v>1920</v>
+        <v>1934</v>
       </c>
       <c r="D110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -2531,13 +2531,13 @@
         <v>74</v>
       </c>
       <c r="B111" t="n">
-        <v>0.923745173745174</v>
+        <v>0.930984555984556</v>
       </c>
       <c r="C111" t="n">
-        <v>1917</v>
+        <v>1933</v>
       </c>
       <c r="D111" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2550,13 +2550,13 @@
         <v>75</v>
       </c>
       <c r="B112" t="n">
-        <v>0.921814671814672</v>
+        <v>0.9295366795366795</v>
       </c>
       <c r="C112" t="n">
-        <v>1914</v>
+        <v>1929</v>
       </c>
       <c r="D112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -2569,13 +2569,13 @@
         <v>77</v>
       </c>
       <c r="B113" t="n">
-        <v>0.9208494208494211</v>
+        <v>0.9280888030888031</v>
       </c>
       <c r="C113" t="n">
-        <v>1910</v>
+        <v>1926</v>
       </c>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -2588,13 +2588,13 @@
         <v>78</v>
       </c>
       <c r="B114" t="n">
-        <v>0.9198841698841702</v>
+        <v>0.9276061776061777</v>
       </c>
       <c r="C114" t="n">
-        <v>1908</v>
+        <v>1923</v>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -2607,13 +2607,13 @@
         <v>79</v>
       </c>
       <c r="B115" t="n">
-        <v>0.9174710424710427</v>
+        <v>0.9261583011583012</v>
       </c>
       <c r="C115" t="n">
-        <v>1906</v>
+        <v>1922</v>
       </c>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -2626,10 +2626,10 @@
         <v>80</v>
       </c>
       <c r="B116" t="n">
-        <v>0.9165057915057918</v>
+        <v>0.9251930501930503</v>
       </c>
       <c r="C116" t="n">
-        <v>1901</v>
+        <v>1919</v>
       </c>
       <c r="D116" t="n">
         <v>2</v>
@@ -2645,13 +2645,13 @@
         <v>81</v>
       </c>
       <c r="B117" t="n">
-        <v>0.9150579150579153</v>
+        <v>0.9247104247104247</v>
       </c>
       <c r="C117" t="n">
-        <v>1899</v>
+        <v>1917</v>
       </c>
       <c r="D117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         <v>82</v>
       </c>
       <c r="B118" t="n">
-        <v>0.9140926640926643</v>
+        <v>0.9237451737451738</v>
       </c>
       <c r="C118" t="n">
-        <v>1896</v>
+        <v>1916</v>
       </c>
       <c r="D118" t="n">
         <v>2</v>
@@ -2683,13 +2683,13 @@
         <v>83</v>
       </c>
       <c r="B119" t="n">
-        <v>0.9131274131274133</v>
+        <v>0.9232625482625484</v>
       </c>
       <c r="C119" t="n">
-        <v>1894</v>
+        <v>1914</v>
       </c>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -2702,13 +2702,13 @@
         <v>84</v>
       </c>
       <c r="B120" t="n">
-        <v>0.9126447876447878</v>
+        <v>0.9222972972972974</v>
       </c>
       <c r="C120" t="n">
-        <v>1892</v>
+        <v>1913</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -2721,13 +2721,13 @@
         <v>85</v>
       </c>
       <c r="B121" t="n">
-        <v>0.9116795366795368</v>
+        <v>0.9218146718146719</v>
       </c>
       <c r="C121" t="n">
-        <v>1891</v>
+        <v>1911</v>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -2740,10 +2740,10 @@
         <v>86</v>
       </c>
       <c r="B122" t="n">
-        <v>0.9107142857142859</v>
+        <v>0.920849420849421</v>
       </c>
       <c r="C122" t="n">
-        <v>1889</v>
+        <v>1910</v>
       </c>
       <c r="D122" t="n">
         <v>2</v>
@@ -2759,13 +2759,13 @@
         <v>87</v>
       </c>
       <c r="B123" t="n">
-        <v>0.9092664092664094</v>
+        <v>0.9189189189189191</v>
       </c>
       <c r="C123" t="n">
-        <v>1887</v>
+        <v>1908</v>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>88</v>
       </c>
       <c r="B124" t="n">
-        <v>0.905888030888031</v>
+        <v>0.9160231660231662</v>
       </c>
       <c r="C124" t="n">
-        <v>1884</v>
+        <v>1904</v>
       </c>
       <c r="D124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -2797,10 +2797,10 @@
         <v>89</v>
       </c>
       <c r="B125" t="n">
-        <v>0.9039575289575291</v>
+        <v>0.9140926640926643</v>
       </c>
       <c r="C125" t="n">
-        <v>1877</v>
+        <v>1898</v>
       </c>
       <c r="D125" t="n">
         <v>4</v>
@@ -2816,13 +2816,13 @@
         <v>90</v>
       </c>
       <c r="B126" t="n">
-        <v>0.9025096525096528</v>
+        <v>0.9131274131274133</v>
       </c>
       <c r="C126" t="n">
-        <v>1873</v>
+        <v>1894</v>
       </c>
       <c r="D126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -2835,13 +2835,13 @@
         <v>91</v>
       </c>
       <c r="B127" t="n">
-        <v>0.9020270270270273</v>
+        <v>0.9121621621621623</v>
       </c>
       <c r="C127" t="n">
-        <v>1870</v>
+        <v>1892</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -2854,10 +2854,10 @@
         <v>92</v>
       </c>
       <c r="B128" t="n">
-        <v>0.9010617760617764</v>
+        <v>0.9111969111969113</v>
       </c>
       <c r="C128" t="n">
-        <v>1869</v>
+        <v>1890</v>
       </c>
       <c r="D128" t="n">
         <v>2</v>
@@ -2873,13 +2873,13 @@
         <v>93</v>
       </c>
       <c r="B129" t="n">
-        <v>0.8991312741312745</v>
+        <v>0.9107142857142858</v>
       </c>
       <c r="C129" t="n">
-        <v>1867</v>
+        <v>1888</v>
       </c>
       <c r="D129" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -2892,13 +2892,13 @@
         <v>95</v>
       </c>
       <c r="B130" t="n">
-        <v>0.8981660231660235</v>
+        <v>0.9092664092664093</v>
       </c>
       <c r="C130" t="n">
-        <v>1863</v>
+        <v>1887</v>
       </c>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         <v>96</v>
       </c>
       <c r="B131" t="n">
-        <v>0.897683397683398</v>
+        <v>0.9087837837837838</v>
       </c>
       <c r="C131" t="n">
-        <v>1861</v>
+        <v>1884</v>
       </c>
       <c r="D131" t="n">
         <v>1</v>
@@ -2930,13 +2930,13 @@
         <v>97</v>
       </c>
       <c r="B132" t="n">
-        <v>0.8957528957528961</v>
+        <v>0.9073359073359073</v>
       </c>
       <c r="C132" t="n">
-        <v>1860</v>
+        <v>1883</v>
       </c>
       <c r="D132" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -2949,10 +2949,10 @@
         <v>98</v>
       </c>
       <c r="B133" t="n">
-        <v>0.8952702702702706</v>
+        <v>0.9068532818532818</v>
       </c>
       <c r="C133" t="n">
-        <v>1856</v>
+        <v>1880</v>
       </c>
       <c r="D133" t="n">
         <v>1</v>
@@ -2968,13 +2968,13 @@
         <v>99</v>
       </c>
       <c r="B134" t="n">
-        <v>0.8947876447876451</v>
+        <v>0.9058880308880308</v>
       </c>
       <c r="C134" t="n">
-        <v>1855</v>
+        <v>1879</v>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -2984,16 +2984,16 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B135" t="n">
-        <v>0.8943050193050196</v>
+        <v>0.9049227799227799</v>
       </c>
       <c r="C135" t="n">
-        <v>1854</v>
+        <v>1877</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -3003,13 +3003,13 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B136" t="n">
-        <v>0.8928571428571431</v>
+        <v>0.9034749034749034</v>
       </c>
       <c r="C136" t="n">
-        <v>1853</v>
+        <v>1875</v>
       </c>
       <c r="D136" t="n">
         <v>3</v>
@@ -3022,16 +3022,16 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B137" t="n">
-        <v>0.8918918918918922</v>
+        <v>0.902027027027027</v>
       </c>
       <c r="C137" t="n">
-        <v>1850</v>
+        <v>1872</v>
       </c>
       <c r="D137" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -3041,16 +3041,16 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B138" t="n">
-        <v>0.8904440154440157</v>
+        <v>0.900096525096525</v>
       </c>
       <c r="C138" t="n">
-        <v>1848</v>
+        <v>1869</v>
       </c>
       <c r="D138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -3060,16 +3060,16 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B139" t="n">
-        <v>0.8899613899613903</v>
+        <v>0.8976833976833977</v>
       </c>
       <c r="C139" t="n">
-        <v>1845</v>
+        <v>1865</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -3079,16 +3079,16 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B140" t="n">
-        <v>0.8870656370656373</v>
+        <v>0.8967181467181466</v>
       </c>
       <c r="C140" t="n">
-        <v>1844</v>
+        <v>1860</v>
       </c>
       <c r="D140" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -3098,16 +3098,16 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B141" t="n">
-        <v>0.8861003861003864</v>
+        <v>0.8938223938223937</v>
       </c>
       <c r="C141" t="n">
-        <v>1838</v>
+        <v>1858</v>
       </c>
       <c r="D141" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -3117,16 +3117,16 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B142" t="n">
-        <v>0.8832046332046336</v>
+        <v>0.8923745173745172</v>
       </c>
       <c r="C142" t="n">
-        <v>1836</v>
+        <v>1852</v>
       </c>
       <c r="D142" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -3136,16 +3136,16 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B143" t="n">
-        <v>0.8827220077220082</v>
+        <v>0.8914092664092662</v>
       </c>
       <c r="C143" t="n">
-        <v>1830</v>
+        <v>1849</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -3155,13 +3155,13 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B144" t="n">
-        <v>0.8812741312741317</v>
+        <v>0.8899613899613897</v>
       </c>
       <c r="C144" t="n">
-        <v>1829</v>
+        <v>1847</v>
       </c>
       <c r="D144" t="n">
         <v>3</v>
@@ -3174,13 +3174,13 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B145" t="n">
-        <v>0.8798262548262552</v>
+        <v>0.8885135135135133</v>
       </c>
       <c r="C145" t="n">
-        <v>1826</v>
+        <v>1844</v>
       </c>
       <c r="D145" t="n">
         <v>3</v>
@@ -3193,16 +3193,16 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B146" t="n">
-        <v>0.8793436293436298</v>
+        <v>0.8861003861003858</v>
       </c>
       <c r="C146" t="n">
-        <v>1823</v>
+        <v>1841</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -3212,16 +3212,16 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B147" t="n">
-        <v>0.8778957528957533</v>
+        <v>0.8856177606177602</v>
       </c>
       <c r="C147" t="n">
-        <v>1822</v>
+        <v>1836</v>
       </c>
       <c r="D147" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B148" t="n">
-        <v>0.8764478764478768</v>
+        <v>0.8846525096525092</v>
       </c>
       <c r="C148" t="n">
-        <v>1819</v>
+        <v>1835</v>
       </c>
       <c r="D148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -3250,16 +3250,16 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B149" t="n">
-        <v>0.8759652509652514</v>
+        <v>0.8836872586872582</v>
       </c>
       <c r="C149" t="n">
-        <v>1816</v>
+        <v>1833</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -3269,16 +3269,16 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B150" t="n">
-        <v>0.8750000000000004</v>
+        <v>0.8817567567567562</v>
       </c>
       <c r="C150" t="n">
-        <v>1815</v>
+        <v>1831</v>
       </c>
       <c r="D150" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -3288,16 +3288,16 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B151" t="n">
-        <v>0.8745173745173749</v>
+        <v>0.8798262548262543</v>
       </c>
       <c r="C151" t="n">
-        <v>1813</v>
+        <v>1827</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -3307,16 +3307,16 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B152" t="n">
-        <v>0.8730694980694985</v>
+        <v>0.8793436293436289</v>
       </c>
       <c r="C152" t="n">
-        <v>1812</v>
+        <v>1823</v>
       </c>
       <c r="D152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -3326,16 +3326,16 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B153" t="n">
-        <v>0.8711389961389966</v>
+        <v>0.8788610038610033</v>
       </c>
       <c r="C153" t="n">
-        <v>1809</v>
+        <v>1822</v>
       </c>
       <c r="D153" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -3345,16 +3345,16 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B154" t="n">
-        <v>0.8696911196911201</v>
+        <v>0.8783783783783778</v>
       </c>
       <c r="C154" t="n">
-        <v>1805</v>
+        <v>1821</v>
       </c>
       <c r="D154" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -3364,16 +3364,16 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B155" t="n">
-        <v>0.8692084942084947</v>
+        <v>0.8769305019305014</v>
       </c>
       <c r="C155" t="n">
-        <v>1802</v>
+        <v>1820</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -3383,16 +3383,16 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B156" t="n">
-        <v>0.8682432432432436</v>
+        <v>0.8764478764478759</v>
       </c>
       <c r="C156" t="n">
-        <v>1801</v>
+        <v>1817</v>
       </c>
       <c r="D156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -3402,16 +3402,16 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B157" t="n">
-        <v>0.8658301158301163</v>
+        <v>0.875482625482625</v>
       </c>
       <c r="C157" t="n">
-        <v>1799</v>
+        <v>1816</v>
       </c>
       <c r="D157" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -3421,16 +3421,16 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B158" t="n">
-        <v>0.8643822393822398</v>
+        <v>0.874517374517374</v>
       </c>
       <c r="C158" t="n">
-        <v>1794</v>
+        <v>1814</v>
       </c>
       <c r="D158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -3440,16 +3440,16 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B159" t="n">
-        <v>0.8634169884169888</v>
+        <v>0.8740347490347485</v>
       </c>
       <c r="C159" t="n">
-        <v>1791</v>
+        <v>1812</v>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -3459,13 +3459,13 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B160" t="n">
-        <v>0.8629343629343633</v>
+        <v>0.873552123552123</v>
       </c>
       <c r="C160" t="n">
-        <v>1789</v>
+        <v>1811</v>
       </c>
       <c r="D160" t="n">
         <v>1</v>
@@ -3478,16 +3478,16 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B161" t="n">
-        <v>0.8624517374517379</v>
+        <v>0.871621621621621</v>
       </c>
       <c r="C161" t="n">
-        <v>1788</v>
+        <v>1810</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -3497,16 +3497,16 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B162" t="n">
-        <v>0.861486486486487</v>
+        <v>0.8711389961389956</v>
       </c>
       <c r="C162" t="n">
-        <v>1787</v>
+        <v>1806</v>
       </c>
       <c r="D162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -3516,13 +3516,13 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B163" t="n">
-        <v>0.8610038610038615</v>
+        <v>0.8706563706563701</v>
       </c>
       <c r="C163" t="n">
-        <v>1785</v>
+        <v>1805</v>
       </c>
       <c r="D163" t="n">
         <v>1</v>
@@ -3535,16 +3535,16 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B164" t="n">
-        <v>0.860521235521236</v>
+        <v>0.8692084942084937</v>
       </c>
       <c r="C164" t="n">
-        <v>1784</v>
+        <v>1804</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -3554,16 +3554,16 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B165" t="n">
-        <v>0.8590733590733597</v>
+        <v>0.8672779922779917</v>
       </c>
       <c r="C165" t="n">
-        <v>1783</v>
+        <v>1801</v>
       </c>
       <c r="D165" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B166" t="n">
-        <v>0.8576254826254832</v>
+        <v>0.8658301158301153</v>
       </c>
       <c r="C166" t="n">
-        <v>1780</v>
+        <v>1797</v>
       </c>
       <c r="D166" t="n">
         <v>3</v>
@@ -3592,16 +3592,16 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B167" t="n">
-        <v>0.8571428571428578</v>
+        <v>0.8634169884169879</v>
       </c>
       <c r="C167" t="n">
-        <v>1777</v>
+        <v>1794</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -3611,16 +3611,16 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B168" t="n">
-        <v>0.8561776061776067</v>
+        <v>0.861486486486486</v>
       </c>
       <c r="C168" t="n">
-        <v>1776</v>
+        <v>1789</v>
       </c>
       <c r="D168" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -3630,13 +3630,13 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B169" t="n">
-        <v>0.8547297297297303</v>
+        <v>0.8600386100386095</v>
       </c>
       <c r="C169" t="n">
-        <v>1774</v>
+        <v>1785</v>
       </c>
       <c r="D169" t="n">
         <v>3</v>
@@ -3649,16 +3649,16 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B170" t="n">
-        <v>0.8532818532818538</v>
+        <v>0.8595559845559839</v>
       </c>
       <c r="C170" t="n">
-        <v>1771</v>
+        <v>1782</v>
       </c>
       <c r="D170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -3671,10 +3671,10 @@
         <v>142</v>
       </c>
       <c r="B171" t="n">
-        <v>0.8518339768339773</v>
+        <v>0.8581081081081074</v>
       </c>
       <c r="C171" t="n">
-        <v>1768</v>
+        <v>1781</v>
       </c>
       <c r="D171" t="n">
         <v>3</v>
@@ -3690,13 +3690,13 @@
         <v>143</v>
       </c>
       <c r="B172" t="n">
-        <v>0.8494208494208498</v>
+        <v>0.8566602316602311</v>
       </c>
       <c r="C172" t="n">
-        <v>1765</v>
+        <v>1778</v>
       </c>
       <c r="D172" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -3706,16 +3706,16 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B173" t="n">
-        <v>0.8484555984555989</v>
+        <v>0.8561776061776056</v>
       </c>
       <c r="C173" t="n">
-        <v>1760</v>
+        <v>1775</v>
       </c>
       <c r="D173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -3728,10 +3728,10 @@
         <v>146</v>
       </c>
       <c r="B174" t="n">
-        <v>0.8474903474903479</v>
+        <v>0.8552123552123547</v>
       </c>
       <c r="C174" t="n">
-        <v>1758</v>
+        <v>1774</v>
       </c>
       <c r="D174" t="n">
         <v>2</v>
@@ -3744,16 +3744,16 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B175" t="n">
-        <v>0.8470077220077225</v>
+        <v>0.8542471042471038</v>
       </c>
       <c r="C175" t="n">
-        <v>1756</v>
+        <v>1772</v>
       </c>
       <c r="D175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -3763,16 +3763,16 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B176" t="n">
-        <v>0.8465250965250969</v>
+        <v>0.8532818532818529</v>
       </c>
       <c r="C176" t="n">
-        <v>1755</v>
+        <v>1770</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -3782,16 +3782,16 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B177" t="n">
-        <v>0.845559845559846</v>
+        <v>0.8527992277992275</v>
       </c>
       <c r="C177" t="n">
-        <v>1754</v>
+        <v>1768</v>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -3801,16 +3801,16 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B178" t="n">
-        <v>0.844594594594595</v>
+        <v>0.852316602316602</v>
       </c>
       <c r="C178" t="n">
-        <v>1752</v>
+        <v>1767</v>
       </c>
       <c r="D178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -3820,16 +3820,16 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B179" t="n">
-        <v>0.8436293436293441</v>
+        <v>0.8518339768339765</v>
       </c>
       <c r="C179" t="n">
-        <v>1750</v>
+        <v>1766</v>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -3839,16 +3839,16 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B180" t="n">
-        <v>0.8431467181467186</v>
+        <v>0.8503861003861001</v>
       </c>
       <c r="C180" t="n">
-        <v>1748</v>
+        <v>1765</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -3858,16 +3858,16 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B181" t="n">
-        <v>0.8421814671814677</v>
+        <v>0.8489382239382236</v>
       </c>
       <c r="C181" t="n">
-        <v>1747</v>
+        <v>1762</v>
       </c>
       <c r="D181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -3877,13 +3877,13 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B182" t="n">
-        <v>0.8416988416988422</v>
+        <v>0.8484555984555981</v>
       </c>
       <c r="C182" t="n">
-        <v>1745</v>
+        <v>1759</v>
       </c>
       <c r="D182" t="n">
         <v>1</v>
@@ -3896,13 +3896,13 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B183" t="n">
-        <v>0.8407335907335913</v>
+        <v>0.8474903474903471</v>
       </c>
       <c r="C183" t="n">
-        <v>1744</v>
+        <v>1758</v>
       </c>
       <c r="D183" t="n">
         <v>2</v>
@@ -3915,16 +3915,16 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B184" t="n">
-        <v>0.8402509652509658</v>
+        <v>0.8455598455598452</v>
       </c>
       <c r="C184" t="n">
-        <v>1742</v>
+        <v>1756</v>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -3934,16 +3934,16 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B185" t="n">
-        <v>0.8388030888030894</v>
+        <v>0.8421814671814668</v>
       </c>
       <c r="C185" t="n">
-        <v>1741</v>
+        <v>1752</v>
       </c>
       <c r="D185" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -3953,16 +3953,16 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B186" t="n">
-        <v>0.8383204633204639</v>
+        <v>0.8402509652509649</v>
       </c>
       <c r="C186" t="n">
-        <v>1738</v>
+        <v>1745</v>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -3972,16 +3972,16 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B187" t="n">
-        <v>0.8349420849420855</v>
+        <v>0.8397683397683394</v>
       </c>
       <c r="C187" t="n">
-        <v>1737</v>
+        <v>1741</v>
       </c>
       <c r="D187" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -3991,16 +3991,16 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B188" t="n">
-        <v>0.8330115830115836</v>
+        <v>0.8388030888030885</v>
       </c>
       <c r="C188" t="n">
-        <v>1730</v>
+        <v>1740</v>
       </c>
       <c r="D188" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -4010,16 +4010,16 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B189" t="n">
-        <v>0.8320463320463327</v>
+        <v>0.8368725868725866</v>
       </c>
       <c r="C189" t="n">
-        <v>1726</v>
+        <v>1738</v>
       </c>
       <c r="D189" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -4029,16 +4029,16 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B190" t="n">
-        <v>0.8310810810810818</v>
+        <v>0.8344594594594592</v>
       </c>
       <c r="C190" t="n">
-        <v>1724</v>
+        <v>1734</v>
       </c>
       <c r="D190" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -4048,13 +4048,13 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B191" t="n">
-        <v>0.8305984555984564</v>
+        <v>0.8339768339768338</v>
       </c>
       <c r="C191" t="n">
-        <v>1722</v>
+        <v>1729</v>
       </c>
       <c r="D191" t="n">
         <v>1</v>
@@ -4067,16 +4067,16 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B192" t="n">
-        <v>0.8291505791505799</v>
+        <v>0.8334942084942083</v>
       </c>
       <c r="C192" t="n">
-        <v>1721</v>
+        <v>1728</v>
       </c>
       <c r="D192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -4086,13 +4086,13 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B193" t="n">
-        <v>0.8286679536679544</v>
+        <v>0.8330115830115828</v>
       </c>
       <c r="C193" t="n">
-        <v>1718</v>
+        <v>1727</v>
       </c>
       <c r="D193" t="n">
         <v>1</v>
@@ -4105,13 +4105,13 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B194" t="n">
-        <v>0.8277027027027035</v>
+        <v>0.8320463320463319</v>
       </c>
       <c r="C194" t="n">
-        <v>1717</v>
+        <v>1726</v>
       </c>
       <c r="D194" t="n">
         <v>2</v>
@@ -4124,16 +4124,16 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B195" t="n">
-        <v>0.8272200772200781</v>
+        <v>0.831081081081081</v>
       </c>
       <c r="C195" t="n">
-        <v>1715</v>
+        <v>1724</v>
       </c>
       <c r="D195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -4143,16 +4143,16 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B196" t="n">
-        <v>0.826254826254827</v>
+        <v>0.8305984555984556</v>
       </c>
       <c r="C196" t="n">
-        <v>1714</v>
+        <v>1722</v>
       </c>
       <c r="D196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -4162,16 +4162,16 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B197" t="n">
-        <v>0.8252895752895761</v>
+        <v>0.8301158301158301</v>
       </c>
       <c r="C197" t="n">
-        <v>1712</v>
+        <v>1721</v>
       </c>
       <c r="D197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -4181,13 +4181,13 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B198" t="n">
-        <v>0.8243243243243252</v>
+        <v>0.8291505791505791</v>
       </c>
       <c r="C198" t="n">
-        <v>1710</v>
+        <v>1720</v>
       </c>
       <c r="D198" t="n">
         <v>2</v>
@@ -4200,16 +4200,16 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B199" t="n">
-        <v>0.8228764478764489</v>
+        <v>0.8281853281853281</v>
       </c>
       <c r="C199" t="n">
-        <v>1708</v>
+        <v>1718</v>
       </c>
       <c r="D199" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -4219,54 +4219,54 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="B200" t="n">
-        <v>0.8219111969111978</v>
+        <v>1</v>
       </c>
       <c r="C200" t="n">
-        <v>1705</v>
+        <v>2072</v>
       </c>
       <c r="D200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Medium predicted risk</t>
+          <t>High predicted risk</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>180</v>
+        <v>0.5</v>
       </c>
       <c r="B201" t="n">
-        <v>0.8209459459459469</v>
+        <v>0.9961389961389961</v>
       </c>
       <c r="C201" t="n">
-        <v>1703</v>
+        <v>2072</v>
       </c>
       <c r="D201" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Medium predicted risk</t>
+          <t>High predicted risk</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B202" t="n">
-        <v>1</v>
+        <v>0.9816602316602316</v>
       </c>
       <c r="C202" t="n">
-        <v>2072</v>
+        <v>2064</v>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -4276,16 +4276,16 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="B203" t="n">
-        <v>0.9951737451737451</v>
+        <v>0.9647683397683398</v>
       </c>
       <c r="C203" t="n">
-        <v>2072</v>
+        <v>2034</v>
       </c>
       <c r="D203" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -4295,13 +4295,13 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B204" t="n">
-        <v>0.9806949806949806</v>
+        <v>0.9502895752895753</v>
       </c>
       <c r="C204" t="n">
-        <v>2062</v>
+        <v>1999</v>
       </c>
       <c r="D204" t="n">
         <v>30</v>
@@ -4314,16 +4314,16 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B205" t="n">
-        <v>0.9638030888030887</v>
+        <v>0.9411196911196911</v>
       </c>
       <c r="C205" t="n">
-        <v>2032</v>
+        <v>1969</v>
       </c>
       <c r="D205" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -4333,16 +4333,16 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B206" t="n">
-        <v>0.9493243243243242</v>
+        <v>0.9295366795366794</v>
       </c>
       <c r="C206" t="n">
-        <v>1997</v>
+        <v>1950</v>
       </c>
       <c r="D206" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -4352,16 +4352,16 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B207" t="n">
-        <v>0.9401544401544401</v>
+        <v>0.9150579150579149</v>
       </c>
       <c r="C207" t="n">
-        <v>1967</v>
+        <v>1926</v>
       </c>
       <c r="D207" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -4371,16 +4371,16 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B208" t="n">
-        <v>0.9285714285714285</v>
+        <v>0.9005791505791504</v>
       </c>
       <c r="C208" t="n">
-        <v>1948</v>
+        <v>1896</v>
       </c>
       <c r="D208" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -4390,16 +4390,16 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B209" t="n">
-        <v>0.914092664092664</v>
+        <v>0.8889961389961388</v>
       </c>
       <c r="C209" t="n">
-        <v>1924</v>
+        <v>1866</v>
       </c>
       <c r="D209" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -4409,16 +4409,16 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B210" t="n">
-        <v>0.901061776061776</v>
+        <v>0.8745173745173743</v>
       </c>
       <c r="C210" t="n">
-        <v>1894</v>
+        <v>1842</v>
       </c>
       <c r="D210" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -4428,16 +4428,16 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B211" t="n">
-        <v>0.88996138996139</v>
+        <v>0.8629343629343628</v>
       </c>
       <c r="C211" t="n">
-        <v>1867</v>
+        <v>1812</v>
       </c>
       <c r="D211" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -4447,16 +4447,16 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B212" t="n">
-        <v>0.8759652509652509</v>
+        <v>0.8513513513513512</v>
       </c>
       <c r="C212" t="n">
-        <v>1844</v>
+        <v>1788</v>
       </c>
       <c r="D212" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -4466,16 +4466,16 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B213" t="n">
-        <v>0.8643822393822392</v>
+        <v>0.8416988416988416</v>
       </c>
       <c r="C213" t="n">
-        <v>1815</v>
+        <v>1764</v>
       </c>
       <c r="D213" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -4485,16 +4485,16 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B214" t="n">
-        <v>0.8527992277992277</v>
+        <v>0.8344594594594593</v>
       </c>
       <c r="C214" t="n">
-        <v>1791</v>
+        <v>1744</v>
       </c>
       <c r="D214" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -4504,16 +4504,16 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B215" t="n">
-        <v>0.844111969111969</v>
+        <v>0.8185328185328183</v>
       </c>
       <c r="C215" t="n">
-        <v>1767</v>
+        <v>1729</v>
       </c>
       <c r="D215" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -4523,16 +4523,16 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B216" t="n">
-        <v>0.8373552123552122</v>
+        <v>0.8069498069498067</v>
       </c>
       <c r="C216" t="n">
-        <v>1749</v>
+        <v>1696</v>
       </c>
       <c r="D216" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -4542,16 +4542,16 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B217" t="n">
-        <v>0.8214285714285712</v>
+        <v>0.799227799227799</v>
       </c>
       <c r="C217" t="n">
-        <v>1735</v>
+        <v>1672</v>
       </c>
       <c r="D217" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -4561,16 +4561,16 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B218" t="n">
-        <v>0.8103281853281851</v>
+        <v>0.7861969111969109</v>
       </c>
       <c r="C218" t="n">
-        <v>1702</v>
+        <v>1656</v>
       </c>
       <c r="D218" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
+        <v>18</v>
+      </c>
+      <c r="B219" t="n">
+        <v>0.7784749034749032</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1629</v>
+      </c>
+      <c r="D219" t="n">
         <v>16</v>
-      </c>
-      <c r="B219" t="n">
-        <v>0.8021235521235519</v>
-      </c>
-      <c r="C219" t="n">
-        <v>1679</v>
-      </c>
-      <c r="D219" t="n">
-        <v>17</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -4599,16 +4599,16 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B220" t="n">
-        <v>0.7890926640926639</v>
+        <v>0.7697876447876445</v>
       </c>
       <c r="C220" t="n">
-        <v>1662</v>
+        <v>1613</v>
       </c>
       <c r="D220" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -4618,16 +4618,16 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B221" t="n">
-        <v>0.7808880308880306</v>
+        <v>0.7625482625482622</v>
       </c>
       <c r="C221" t="n">
-        <v>1635</v>
+        <v>1595</v>
       </c>
       <c r="D221" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -4637,16 +4637,16 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
+        <v>21</v>
+      </c>
+      <c r="B222" t="n">
+        <v>0.7533783783783781</v>
+      </c>
+      <c r="C222" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D222" t="n">
         <v>19</v>
-      </c>
-      <c r="B222" t="n">
-        <v>0.7722007722007719</v>
-      </c>
-      <c r="C222" t="n">
-        <v>1618</v>
-      </c>
-      <c r="D222" t="n">
-        <v>18</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -4656,13 +4656,13 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B223" t="n">
-        <v>0.7644787644787642</v>
+        <v>0.7456563706563704</v>
       </c>
       <c r="C223" t="n">
-        <v>1600</v>
+        <v>1561</v>
       </c>
       <c r="D223" t="n">
         <v>16</v>
@@ -4675,16 +4675,16 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B224" t="n">
-        <v>0.756274131274131</v>
+        <v>0.7316602316602314</v>
       </c>
       <c r="C224" t="n">
-        <v>1584</v>
+        <v>1545</v>
       </c>
       <c r="D224" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -4694,16 +4694,16 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B225" t="n">
-        <v>0.7485521235521233</v>
+        <v>0.7249034749034747</v>
       </c>
       <c r="C225" t="n">
-        <v>1567</v>
+        <v>1516</v>
       </c>
       <c r="D225" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -4713,16 +4713,16 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B226" t="n">
-        <v>0.7345559845559843</v>
+        <v>0.7128378378378376</v>
       </c>
       <c r="C226" t="n">
-        <v>1551</v>
+        <v>1502</v>
       </c>
       <c r="D226" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -4732,16 +4732,16 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B227" t="n">
-        <v>0.7277992277992275</v>
+        <v>0.7080115830115827</v>
       </c>
       <c r="C227" t="n">
-        <v>1522</v>
+        <v>1477</v>
       </c>
       <c r="D227" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -4751,16 +4751,16 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B228" t="n">
-        <v>0.7157335907335904</v>
+        <v>0.700289575289575</v>
       </c>
       <c r="C228" t="n">
-        <v>1508</v>
+        <v>1467</v>
       </c>
       <c r="D228" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -4770,16 +4770,16 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B229" t="n">
-        <v>0.7109073359073357</v>
+        <v>0.6887065637065635</v>
       </c>
       <c r="C229" t="n">
-        <v>1483</v>
+        <v>1451</v>
       </c>
       <c r="D229" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -4789,16 +4789,16 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B230" t="n">
-        <v>0.7041505791505789</v>
+        <v>0.6829150579150577</v>
       </c>
       <c r="C230" t="n">
-        <v>1473</v>
+        <v>1427</v>
       </c>
       <c r="D230" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -4808,16 +4808,16 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B231" t="n">
-        <v>0.6925675675675673</v>
+        <v>0.6747104247104245</v>
       </c>
       <c r="C231" t="n">
-        <v>1459</v>
+        <v>1415</v>
       </c>
       <c r="D231" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -4827,16 +4827,16 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B232" t="n">
-        <v>0.687258687258687</v>
+        <v>0.6679536679536677</v>
       </c>
       <c r="C232" t="n">
-        <v>1435</v>
+        <v>1398</v>
       </c>
       <c r="D232" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -4846,16 +4846,16 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B233" t="n">
-        <v>0.6790540540540538</v>
+        <v>0.66023166023166</v>
       </c>
       <c r="C233" t="n">
-        <v>1424</v>
+        <v>1384</v>
       </c>
       <c r="D233" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -4865,16 +4865,16 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B234" t="n">
-        <v>0.6722972972972971</v>
+        <v>0.6563706563706562</v>
       </c>
       <c r="C234" t="n">
-        <v>1407</v>
+        <v>1368</v>
       </c>
       <c r="D234" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -4884,16 +4884,16 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B235" t="n">
-        <v>0.6660231660231659</v>
+        <v>0.647200772200772</v>
       </c>
       <c r="C235" t="n">
-        <v>1393</v>
+        <v>1360</v>
       </c>
       <c r="D235" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -4903,13 +4903,13 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B236" t="n">
-        <v>0.6616795366795366</v>
+        <v>0.6428571428571427</v>
       </c>
       <c r="C236" t="n">
-        <v>1380</v>
+        <v>1341</v>
       </c>
       <c r="D236" t="n">
         <v>9</v>
@@ -4922,16 +4922,16 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B237" t="n">
-        <v>0.6529922779922779</v>
+        <v>0.6346525096525095</v>
       </c>
       <c r="C237" t="n">
-        <v>1371</v>
+        <v>1332</v>
       </c>
       <c r="D237" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -4941,16 +4941,16 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B238" t="n">
-        <v>0.649131274131274</v>
+        <v>0.6298262548262548</v>
       </c>
       <c r="C238" t="n">
-        <v>1353</v>
+        <v>1315</v>
       </c>
       <c r="D238" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -4960,13 +4960,13 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B239" t="n">
-        <v>0.6423745173745172</v>
+        <v>0.623069498069498</v>
       </c>
       <c r="C239" t="n">
-        <v>1345</v>
+        <v>1305</v>
       </c>
       <c r="D239" t="n">
         <v>14</v>
@@ -4979,16 +4979,16 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B240" t="n">
-        <v>0.6375482625482624</v>
+        <v>0.6167953667953666</v>
       </c>
       <c r="C240" t="n">
-        <v>1331</v>
+        <v>1291</v>
       </c>
       <c r="D240" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -4998,16 +4998,16 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B241" t="n">
-        <v>0.6317567567567566</v>
+        <v>0.6081081081081079</v>
       </c>
       <c r="C241" t="n">
-        <v>1321</v>
+        <v>1278</v>
       </c>
       <c r="D241" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -5017,16 +5017,16 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B242" t="n">
-        <v>0.6259652509652508</v>
+        <v>0.604247104247104</v>
       </c>
       <c r="C242" t="n">
-        <v>1309</v>
+        <v>1260</v>
       </c>
       <c r="D242" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -5036,16 +5036,16 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B243" t="n">
-        <v>0.6182432432432431</v>
+        <v>0.5979729729729728</v>
       </c>
       <c r="C243" t="n">
-        <v>1297</v>
+        <v>1252</v>
       </c>
       <c r="D243" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -5055,16 +5055,16 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B244" t="n">
-        <v>0.6134169884169882</v>
+        <v>0.5907335907335906</v>
       </c>
       <c r="C244" t="n">
-        <v>1281</v>
+        <v>1239</v>
       </c>
       <c r="D244" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -5074,16 +5074,16 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B245" t="n">
-        <v>0.607142857142857</v>
+        <v>0.5859073359073358</v>
       </c>
       <c r="C245" t="n">
-        <v>1271</v>
+        <v>1224</v>
       </c>
       <c r="D245" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -5093,16 +5093,16 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B246" t="n">
-        <v>0.6003861003861002</v>
+        <v>0.5805984555984555</v>
       </c>
       <c r="C246" t="n">
-        <v>1258</v>
+        <v>1214</v>
       </c>
       <c r="D246" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -5112,16 +5112,16 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B247" t="n">
-        <v>0.5950772200772199</v>
+        <v>0.5762548262548262</v>
       </c>
       <c r="C247" t="n">
-        <v>1244</v>
+        <v>1203</v>
       </c>
       <c r="D247" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -5131,16 +5131,16 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B248" t="n">
-        <v>0.5897683397683395</v>
+        <v>0.5714285714285713</v>
       </c>
       <c r="C248" t="n">
-        <v>1233</v>
+        <v>1194</v>
       </c>
       <c r="D248" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -5150,16 +5150,16 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B249" t="n">
-        <v>0.5844594594594592</v>
+        <v>0.567084942084942</v>
       </c>
       <c r="C249" t="n">
-        <v>1222</v>
+        <v>1184</v>
       </c>
       <c r="D249" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -5169,16 +5169,16 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B250" t="n">
-        <v>0.5796332046332043</v>
+        <v>0.5608108108108106</v>
       </c>
       <c r="C250" t="n">
-        <v>1211</v>
+        <v>1175</v>
       </c>
       <c r="D250" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -5188,16 +5188,16 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B251" t="n">
-        <v>0.575289575289575</v>
+        <v>0.5550193050193049</v>
       </c>
       <c r="C251" t="n">
-        <v>1201</v>
+        <v>1162</v>
       </c>
       <c r="D251" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -5207,16 +5207,16 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B252" t="n">
-        <v>0.5685328185328183</v>
+        <v>0.5506756756756755</v>
       </c>
       <c r="C252" t="n">
-        <v>1192</v>
+        <v>1150</v>
       </c>
       <c r="D252" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -5226,16 +5226,16 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B253" t="n">
-        <v>0.5627413127413126</v>
+        <v>0.5463320463320461</v>
       </c>
       <c r="C253" t="n">
-        <v>1178</v>
+        <v>1141</v>
       </c>
       <c r="D253" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -5245,16 +5245,16 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B254" t="n">
-        <v>0.5583976833976833</v>
+        <v>0.5405405405405403</v>
       </c>
       <c r="C254" t="n">
-        <v>1166</v>
+        <v>1132</v>
       </c>
       <c r="D254" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -5264,16 +5264,16 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B255" t="n">
-        <v>0.5535714285714284</v>
+        <v>0.5342664092664091</v>
       </c>
       <c r="C255" t="n">
-        <v>1157</v>
+        <v>1120</v>
       </c>
       <c r="D255" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -5283,16 +5283,16 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B256" t="n">
-        <v>0.5472972972972971</v>
+        <v>0.5313706563706562</v>
       </c>
       <c r="C256" t="n">
-        <v>1147</v>
+        <v>1107</v>
       </c>
       <c r="D256" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -5302,16 +5302,16 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B257" t="n">
-        <v>0.5415057915057914</v>
+        <v>0.5294401544401542</v>
       </c>
       <c r="C257" t="n">
-        <v>1134</v>
+        <v>1101</v>
       </c>
       <c r="D257" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -5321,16 +5321,16 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B258" t="n">
-        <v>0.5386100386100384</v>
+        <v>0.5250965250965249</v>
       </c>
       <c r="C258" t="n">
-        <v>1122</v>
+        <v>1097</v>
       </c>
       <c r="D258" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -5340,16 +5340,16 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B259" t="n">
-        <v>0.5366795366795365</v>
+        <v>0.5202702702702702</v>
       </c>
       <c r="C259" t="n">
-        <v>1116</v>
+        <v>1088</v>
       </c>
       <c r="D259" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -5359,16 +5359,16 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B260" t="n">
-        <v>0.5323359073359072</v>
+        <v>0.5149613899613898</v>
       </c>
       <c r="C260" t="n">
-        <v>1112</v>
+        <v>1078</v>
       </c>
       <c r="D260" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -5378,16 +5378,16 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B261" t="n">
-        <v>0.5289575289575288</v>
+        <v>0.5135135135135134</v>
       </c>
       <c r="C261" t="n">
-        <v>1103</v>
+        <v>1067</v>
       </c>
       <c r="D261" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -5397,16 +5397,16 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B262" t="n">
-        <v>0.5226833976833976</v>
+        <v>0.510135135135135</v>
       </c>
       <c r="C262" t="n">
-        <v>1096</v>
+        <v>1064</v>
       </c>
       <c r="D262" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -5416,16 +5416,16 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B263" t="n">
-        <v>0.5207528957528956</v>
+        <v>0.5053088803088802</v>
       </c>
       <c r="C263" t="n">
-        <v>1083</v>
+        <v>1057</v>
       </c>
       <c r="D263" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -5435,16 +5435,16 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B264" t="n">
-        <v>0.5178571428571427</v>
+        <v>0.5038610038610037</v>
       </c>
       <c r="C264" t="n">
-        <v>1079</v>
+        <v>1047</v>
       </c>
       <c r="D264" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -5454,16 +5454,16 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B265" t="n">
-        <v>0.5139961389961388</v>
+        <v>0.4995173745173744</v>
       </c>
       <c r="C265" t="n">
-        <v>1073</v>
+        <v>1044</v>
       </c>
       <c r="D265" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -5473,16 +5473,16 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B266" t="n">
-        <v>0.5135135135135134</v>
+        <v>0.4966216216216215</v>
       </c>
       <c r="C266" t="n">
-        <v>1065</v>
+        <v>1035</v>
       </c>
       <c r="D266" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -5492,16 +5492,16 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B267" t="n">
-        <v>0.5091698841698841</v>
+        <v>0.4937258687258687</v>
       </c>
       <c r="C267" t="n">
-        <v>1064</v>
+        <v>1029</v>
       </c>
       <c r="D267" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -5511,16 +5511,16 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B268" t="n">
-        <v>0.5057915057915057</v>
+        <v>0.4893822393822393</v>
       </c>
       <c r="C268" t="n">
-        <v>1055</v>
+        <v>1023</v>
       </c>
       <c r="D268" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -5530,16 +5530,16 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B269" t="n">
-        <v>0.5028957528957527</v>
+        <v>0.4869691119691119</v>
       </c>
       <c r="C269" t="n">
-        <v>1048</v>
+        <v>1014</v>
       </c>
       <c r="D269" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -5549,13 +5549,13 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B270" t="n">
-        <v>0.4985521235521234</v>
+        <v>0.4826254826254825</v>
       </c>
       <c r="C270" t="n">
-        <v>1042</v>
+        <v>1009</v>
       </c>
       <c r="D270" t="n">
         <v>9</v>
@@ -5568,16 +5568,16 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B271" t="n">
-        <v>0.4956563706563705</v>
+        <v>0.4806949806949806</v>
       </c>
       <c r="C271" t="n">
-        <v>1033</v>
+        <v>1000</v>
       </c>
       <c r="D271" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B272" t="n">
-        <v>0.4917953667953666</v>
+        <v>0.4792471042471041</v>
       </c>
       <c r="C272" t="n">
-        <v>1027</v>
+        <v>996</v>
       </c>
       <c r="D272" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -5606,16 +5606,16 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B273" t="n">
-        <v>0.4903474903474901</v>
+        <v>0.4768339768339767</v>
       </c>
       <c r="C273" t="n">
-        <v>1019</v>
+        <v>993</v>
       </c>
       <c r="D273" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -5625,16 +5625,16 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B274" t="n">
-        <v>0.4888996138996137</v>
+        <v>0.4744208494208493</v>
       </c>
       <c r="C274" t="n">
-        <v>1016</v>
+        <v>988</v>
       </c>
       <c r="D274" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -5644,13 +5644,13 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B275" t="n">
-        <v>0.4869691119691118</v>
+        <v>0.4724903474903474</v>
       </c>
       <c r="C275" t="n">
-        <v>1013</v>
+        <v>983</v>
       </c>
       <c r="D275" t="n">
         <v>4</v>
@@ -5663,16 +5663,16 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B276" t="n">
-        <v>0.4840733590733589</v>
+        <v>0.4666988416988416</v>
       </c>
       <c r="C276" t="n">
-        <v>1009</v>
+        <v>979</v>
       </c>
       <c r="D276" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -5682,16 +5682,16 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B277" t="n">
-        <v>0.4816602316602315</v>
+        <v>0.4652509652509652</v>
       </c>
       <c r="C277" t="n">
-        <v>1003</v>
+        <v>967</v>
       </c>
       <c r="D277" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -5701,16 +5701,16 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B278" t="n">
-        <v>0.4763513513513513</v>
+        <v>0.4628378378378378</v>
       </c>
       <c r="C278" t="n">
-        <v>998</v>
+        <v>964</v>
       </c>
       <c r="D278" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -5720,16 +5720,16 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B279" t="n">
-        <v>0.4749034749034748</v>
+        <v>0.4618725868725868</v>
       </c>
       <c r="C279" t="n">
-        <v>987</v>
+        <v>959</v>
       </c>
       <c r="D279" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -5739,13 +5739,13 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B280" t="n">
-        <v>0.472007722007722</v>
+        <v>0.4589768339768339</v>
       </c>
       <c r="C280" t="n">
-        <v>984</v>
+        <v>957</v>
       </c>
       <c r="D280" t="n">
         <v>6</v>
@@ -5758,16 +5758,16 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B281" t="n">
-        <v>0.471042471042471</v>
+        <v>0.4584942084942085</v>
       </c>
       <c r="C281" t="n">
-        <v>978</v>
+        <v>951</v>
       </c>
       <c r="D281" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -5777,16 +5777,16 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B282" t="n">
-        <v>0.4691119691119691</v>
+        <v>0.4555984555984556</v>
       </c>
       <c r="C282" t="n">
-        <v>976</v>
+        <v>950</v>
       </c>
       <c r="D282" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -5796,16 +5796,16 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B283" t="n">
-        <v>0.4686293436293436</v>
+        <v>0.4531853281853281</v>
       </c>
       <c r="C283" t="n">
-        <v>972</v>
+        <v>944</v>
       </c>
       <c r="D283" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -5815,13 +5815,13 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B284" t="n">
-        <v>0.4666988416988417</v>
+        <v>0.4512548262548262</v>
       </c>
       <c r="C284" t="n">
-        <v>971</v>
+        <v>939</v>
       </c>
       <c r="D284" t="n">
         <v>4</v>
@@ -5834,16 +5834,16 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B285" t="n">
-        <v>0.4642857142857142</v>
+        <v>0.4483590733590733</v>
       </c>
       <c r="C285" t="n">
-        <v>967</v>
+        <v>935</v>
       </c>
       <c r="D285" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -5853,16 +5853,16 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B286" t="n">
-        <v>0.4628378378378378</v>
+        <v>0.4464285714285714</v>
       </c>
       <c r="C286" t="n">
-        <v>962</v>
+        <v>929</v>
       </c>
       <c r="D286" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -5872,16 +5872,16 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B287" t="n">
-        <v>0.4594594594594594</v>
+        <v>0.4454633204633204</v>
       </c>
       <c r="C287" t="n">
-        <v>959</v>
+        <v>925</v>
       </c>
       <c r="D287" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -5891,16 +5891,16 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B288" t="n">
-        <v>0.458011583011583</v>
+        <v>0.4444980694980695</v>
       </c>
       <c r="C288" t="n">
-        <v>952</v>
+        <v>923</v>
       </c>
       <c r="D288" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -5910,16 +5910,16 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B289" t="n">
-        <v>0.457046332046332</v>
+        <v>0.4401544401544401</v>
       </c>
       <c r="C289" t="n">
-        <v>949</v>
+        <v>921</v>
       </c>
       <c r="D289" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -5929,13 +5929,13 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B290" t="n">
-        <v>0.456081081081081</v>
+        <v>0.4391891891891891</v>
       </c>
       <c r="C290" t="n">
-        <v>947</v>
+        <v>912</v>
       </c>
       <c r="D290" t="n">
         <v>2</v>
@@ -5948,16 +5948,16 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B291" t="n">
-        <v>0.4522200772200772</v>
+        <v>0.4362934362934363</v>
       </c>
       <c r="C291" t="n">
-        <v>945</v>
+        <v>910</v>
       </c>
       <c r="D291" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -5967,16 +5967,16 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B292" t="n">
-        <v>0.4512548262548262</v>
+        <v>0.4338803088803088</v>
       </c>
       <c r="C292" t="n">
-        <v>937</v>
+        <v>904</v>
       </c>
       <c r="D292" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -5986,16 +5986,16 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B293" t="n">
-        <v>0.4488416988416988</v>
+        <v>0.4329150579150579</v>
       </c>
       <c r="C293" t="n">
-        <v>935</v>
+        <v>899</v>
       </c>
       <c r="D293" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -6005,16 +6005,16 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B294" t="n">
-        <v>0.4459459459459459</v>
+        <v>0.4309845559845559</v>
       </c>
       <c r="C294" t="n">
-        <v>930</v>
+        <v>897</v>
       </c>
       <c r="D294" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -6024,13 +6024,13 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B295" t="n">
-        <v>0.4449806949806949</v>
+        <v>0.430019305019305</v>
       </c>
       <c r="C295" t="n">
-        <v>924</v>
+        <v>893</v>
       </c>
       <c r="D295" t="n">
         <v>2</v>
@@ -6043,16 +6043,16 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B296" t="n">
-        <v>0.444015444015444</v>
+        <v>0.4276061776061776</v>
       </c>
       <c r="C296" t="n">
-        <v>922</v>
+        <v>891</v>
       </c>
       <c r="D296" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -6062,13 +6062,13 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B297" t="n">
-        <v>0.443050193050193</v>
+        <v>0.4266409266409266</v>
       </c>
       <c r="C297" t="n">
-        <v>920</v>
+        <v>886</v>
       </c>
       <c r="D297" t="n">
         <v>2</v>
@@ -6081,13 +6081,13 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B298" t="n">
-        <v>0.4401544401544401</v>
+        <v>0.4237451737451737</v>
       </c>
       <c r="C298" t="n">
-        <v>918</v>
+        <v>884</v>
       </c>
       <c r="D298" t="n">
         <v>6</v>
@@ -6100,16 +6100,16 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B299" t="n">
-        <v>0.4391891891891891</v>
+        <v>0.4222972972972973</v>
       </c>
       <c r="C299" t="n">
-        <v>912</v>
+        <v>878</v>
       </c>
       <c r="D299" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -6119,16 +6119,16 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B300" t="n">
-        <v>0.4372586872586872</v>
+        <v>0.4208494208494208</v>
       </c>
       <c r="C300" t="n">
-        <v>910</v>
+        <v>875</v>
       </c>
       <c r="D300" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -6138,13 +6138,13 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B301" t="n">
-        <v>0.4358108108108107</v>
+        <v>0.4194015444015443</v>
       </c>
       <c r="C301" t="n">
-        <v>906</v>
+        <v>872</v>
       </c>
       <c r="D301" t="n">
         <v>3</v>
@@ -6157,16 +6157,16 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B302" t="n">
-        <v>0.4338803088803088</v>
+        <v>0.4184362934362933</v>
       </c>
       <c r="C302" t="n">
-        <v>903</v>
+        <v>869</v>
       </c>
       <c r="D302" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -6176,16 +6176,16 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B303" t="n">
-        <v>0.4329150579150579</v>
+        <v>0.4169884169884169</v>
       </c>
       <c r="C303" t="n">
-        <v>899</v>
+        <v>867</v>
       </c>
       <c r="D303" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -6195,13 +6195,13 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B304" t="n">
-        <v>0.4319498069498069</v>
+        <v>0.4160231660231659</v>
       </c>
       <c r="C304" t="n">
-        <v>897</v>
+        <v>864</v>
       </c>
       <c r="D304" t="n">
         <v>2</v>
@@ -6214,13 +6214,13 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B305" t="n">
-        <v>0.430019305019305</v>
+        <v>0.414092664092664</v>
       </c>
       <c r="C305" t="n">
-        <v>895</v>
+        <v>862</v>
       </c>
       <c r="D305" t="n">
         <v>4</v>
@@ -6233,13 +6233,13 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B306" t="n">
-        <v>0.429054054054054</v>
+        <v>0.413127413127413</v>
       </c>
       <c r="C306" t="n">
-        <v>891</v>
+        <v>858</v>
       </c>
       <c r="D306" t="n">
         <v>2</v>
@@ -6252,16 +6252,16 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B307" t="n">
-        <v>0.4256756756756756</v>
+        <v>0.4107142857142856</v>
       </c>
       <c r="C307" t="n">
-        <v>889</v>
+        <v>856</v>
       </c>
       <c r="D307" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -6271,16 +6271,16 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B308" t="n">
-        <v>0.4247104247104246</v>
+        <v>0.4092664092664092</v>
       </c>
       <c r="C308" t="n">
-        <v>882</v>
+        <v>851</v>
       </c>
       <c r="D308" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -6290,16 +6290,16 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B309" t="n">
-        <v>0.4222972972972972</v>
+        <v>0.4078185328185328</v>
       </c>
       <c r="C309" t="n">
-        <v>880</v>
+        <v>848</v>
       </c>
       <c r="D309" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -6309,16 +6309,16 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B310" t="n">
-        <v>0.4213320463320462</v>
+        <v>0.4049227799227799</v>
       </c>
       <c r="C310" t="n">
-        <v>875</v>
+        <v>845</v>
       </c>
       <c r="D310" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -6328,13 +6328,13 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B311" t="n">
-        <v>0.4198841698841698</v>
+        <v>0.4034749034749034</v>
       </c>
       <c r="C311" t="n">
-        <v>873</v>
+        <v>839</v>
       </c>
       <c r="D311" t="n">
         <v>3</v>
@@ -6347,16 +6347,16 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B312" t="n">
-        <v>0.4174710424710424</v>
+        <v>0.3996138996138995</v>
       </c>
       <c r="C312" t="n">
-        <v>870</v>
+        <v>836</v>
       </c>
       <c r="D312" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -6366,16 +6366,16 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B313" t="n">
-        <v>0.4160231660231659</v>
+        <v>0.3976833976833976</v>
       </c>
       <c r="C313" t="n">
-        <v>865</v>
+        <v>828</v>
       </c>
       <c r="D313" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -6385,16 +6385,16 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B314" t="n">
-        <v>0.4126447876447876</v>
+        <v>0.3957528957528957</v>
       </c>
       <c r="C314" t="n">
-        <v>862</v>
+        <v>824</v>
       </c>
       <c r="D314" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -6404,16 +6404,16 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B315" t="n">
-        <v>0.4107142857142856</v>
+        <v>0.3943050193050192</v>
       </c>
       <c r="C315" t="n">
-        <v>855</v>
+        <v>820</v>
       </c>
       <c r="D315" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -6423,16 +6423,16 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B316" t="n">
-        <v>0.4073359073359072</v>
+        <v>0.3938223938223938</v>
       </c>
       <c r="C316" t="n">
-        <v>851</v>
+        <v>817</v>
       </c>
       <c r="D316" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -6442,13 +6442,13 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B317" t="n">
-        <v>0.4054054054054053</v>
+        <v>0.3918918918918918</v>
       </c>
       <c r="C317" t="n">
-        <v>844</v>
+        <v>816</v>
       </c>
       <c r="D317" t="n">
         <v>4</v>
@@ -6461,13 +6461,13 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B318" t="n">
-        <v>0.4049227799227799</v>
+        <v>0.3914092664092663</v>
       </c>
       <c r="C318" t="n">
-        <v>840</v>
+        <v>812</v>
       </c>
       <c r="D318" t="n">
         <v>1</v>
@@ -6480,16 +6480,16 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B319" t="n">
-        <v>0.4029922779922779</v>
+        <v>0.3904440154440154</v>
       </c>
       <c r="C319" t="n">
-        <v>839</v>
+        <v>811</v>
       </c>
       <c r="D319" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -6499,16 +6499,16 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B320" t="n">
-        <v>0.402027027027027</v>
+        <v>0.3889961389961389</v>
       </c>
       <c r="C320" t="n">
-        <v>835</v>
+        <v>809</v>
       </c>
       <c r="D320" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -6518,16 +6518,16 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B321" t="n">
-        <v>0.401061776061776</v>
+        <v>0.3875482625482625</v>
       </c>
       <c r="C321" t="n">
-        <v>833</v>
+        <v>806</v>
       </c>
       <c r="D321" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -6537,13 +6537,13 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B322" t="n">
-        <v>0.3996138996138995</v>
+        <v>0.386100386100386</v>
       </c>
       <c r="C322" t="n">
-        <v>831</v>
+        <v>803</v>
       </c>
       <c r="D322" t="n">
         <v>3</v>
@@ -6556,16 +6556,16 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B323" t="n">
-        <v>0.3986486486486486</v>
+        <v>0.3846525096525095</v>
       </c>
       <c r="C323" t="n">
-        <v>828</v>
+        <v>800</v>
       </c>
       <c r="D323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -6575,13 +6575,13 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B324" t="n">
-        <v>0.3976833976833976</v>
+        <v>0.3836872586872586</v>
       </c>
       <c r="C324" t="n">
-        <v>826</v>
+        <v>797</v>
       </c>
       <c r="D324" t="n">
         <v>2</v>
@@ -6594,16 +6594,16 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B325" t="n">
-        <v>0.3972007722007721</v>
+        <v>0.3812741312741311</v>
       </c>
       <c r="C325" t="n">
-        <v>824</v>
+        <v>795</v>
       </c>
       <c r="D325" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -6613,16 +6613,16 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B326" t="n">
-        <v>0.3957528957528957</v>
+        <v>0.3803088803088802</v>
       </c>
       <c r="C326" t="n">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="D326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -6632,16 +6632,16 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B327" t="n">
-        <v>0.3938223938223938</v>
+        <v>0.3793436293436292</v>
       </c>
       <c r="C327" t="n">
-        <v>820</v>
+        <v>788</v>
       </c>
       <c r="D327" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -6651,13 +6651,13 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B328" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.3783783783783782</v>
       </c>
       <c r="C328" t="n">
-        <v>816</v>
+        <v>786</v>
       </c>
       <c r="D328" t="n">
         <v>2</v>
@@ -6670,16 +6670,16 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B329" t="n">
-        <v>0.3918918918918918</v>
+        <v>0.3778957528957527</v>
       </c>
       <c r="C329" t="n">
-        <v>814</v>
+        <v>784</v>
       </c>
       <c r="D329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -6689,16 +6689,16 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B330" t="n">
-        <v>0.3904440154440154</v>
+        <v>0.3769305019305018</v>
       </c>
       <c r="C330" t="n">
-        <v>812</v>
+        <v>783</v>
       </c>
       <c r="D330" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -6708,13 +6708,13 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B331" t="n">
-        <v>0.3894787644787644</v>
+        <v>0.3759652509652508</v>
       </c>
       <c r="C331" t="n">
-        <v>809</v>
+        <v>781</v>
       </c>
       <c r="D331" t="n">
         <v>2</v>
@@ -6727,16 +6727,16 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B332" t="n">
-        <v>0.3885135135135135</v>
+        <v>0.3754826254826253</v>
       </c>
       <c r="C332" t="n">
-        <v>807</v>
+        <v>779</v>
       </c>
       <c r="D332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -6746,16 +6746,16 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B333" t="n">
-        <v>0.3875482625482625</v>
+        <v>0.3740347490347489</v>
       </c>
       <c r="C333" t="n">
-        <v>805</v>
+        <v>778</v>
       </c>
       <c r="D333" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -6765,16 +6765,16 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B334" t="n">
-        <v>0.387065637065637</v>
+        <v>0.372104247104247</v>
       </c>
       <c r="C334" t="n">
-        <v>803</v>
+        <v>775</v>
       </c>
       <c r="D334" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -6784,16 +6784,16 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B335" t="n">
-        <v>0.3851351351351351</v>
+        <v>0.3716216216216215</v>
       </c>
       <c r="C335" t="n">
-        <v>802</v>
+        <v>771</v>
       </c>
       <c r="D335" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -6803,16 +6803,16 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B336" t="n">
-        <v>0.3827220077220077</v>
+        <v>0.3711389961389961</v>
       </c>
       <c r="C336" t="n">
-        <v>798</v>
+        <v>770</v>
       </c>
       <c r="D336" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -6822,16 +6822,16 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B337" t="n">
-        <v>0.3812741312741312</v>
+        <v>0.3701737451737451</v>
       </c>
       <c r="C337" t="n">
-        <v>793</v>
+        <v>769</v>
       </c>
       <c r="D337" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -6841,16 +6841,16 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B338" t="n">
-        <v>0.3793436293436293</v>
+        <v>0.3692084942084942</v>
       </c>
       <c r="C338" t="n">
-        <v>790</v>
+        <v>767</v>
       </c>
       <c r="D338" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -6860,16 +6860,16 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B339" t="n">
-        <v>0.3783783783783783</v>
+        <v>0.3677606177606177</v>
       </c>
       <c r="C339" t="n">
-        <v>786</v>
+        <v>765</v>
       </c>
       <c r="D339" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -6879,16 +6879,16 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B340" t="n">
-        <v>0.3774131274131274</v>
+        <v>0.3663127413127413</v>
       </c>
       <c r="C340" t="n">
-        <v>784</v>
+        <v>762</v>
       </c>
       <c r="D340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -6898,16 +6898,16 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B341" t="n">
-        <v>0.3759652509652509</v>
+        <v>0.3653474903474903</v>
       </c>
       <c r="C341" t="n">
-        <v>782</v>
+        <v>759</v>
       </c>
       <c r="D341" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -6917,16 +6917,16 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B342" t="n">
-        <v>0.374034749034749</v>
+        <v>0.3629343629343629</v>
       </c>
       <c r="C342" t="n">
-        <v>779</v>
+        <v>757</v>
       </c>
       <c r="D342" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -6936,16 +6936,16 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B343" t="n">
-        <v>0.373069498069498</v>
+        <v>0.3610038610038609</v>
       </c>
       <c r="C343" t="n">
-        <v>775</v>
+        <v>752</v>
       </c>
       <c r="D343" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -6955,16 +6955,16 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B344" t="n">
-        <v>0.3716216216216215</v>
+        <v>0.36003861003861</v>
       </c>
       <c r="C344" t="n">
-        <v>773</v>
+        <v>748</v>
       </c>
       <c r="D344" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -6974,16 +6974,16 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B345" t="n">
-        <v>0.3701737451737451</v>
+        <v>0.359073359073359</v>
       </c>
       <c r="C345" t="n">
-        <v>770</v>
+        <v>746</v>
       </c>
       <c r="D345" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -6993,16 +6993,16 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B346" t="n">
-        <v>0.3687258687258687</v>
+        <v>0.3585907335907335</v>
       </c>
       <c r="C346" t="n">
-        <v>767</v>
+        <v>744</v>
       </c>
       <c r="D346" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -7012,16 +7012,16 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B347" t="n">
-        <v>0.3677606177606177</v>
+        <v>0.358108108108108</v>
       </c>
       <c r="C347" t="n">
-        <v>764</v>
+        <v>743</v>
       </c>
       <c r="D347" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -7031,16 +7031,16 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B348" t="n">
-        <v>0.3672779922779922</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="C348" t="n">
-        <v>762</v>
+        <v>742</v>
       </c>
       <c r="D348" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -7050,13 +7050,13 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B349" t="n">
-        <v>0.3667953667953667</v>
+        <v>0.3566602316602316</v>
       </c>
       <c r="C349" t="n">
-        <v>761</v>
+        <v>740</v>
       </c>
       <c r="D349" t="n">
         <v>1</v>
@@ -7069,13 +7069,13 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B350" t="n">
-        <v>0.3663127413127413</v>
+        <v>0.3561776061776061</v>
       </c>
       <c r="C350" t="n">
-        <v>760</v>
+        <v>739</v>
       </c>
       <c r="D350" t="n">
         <v>1</v>
@@ -7088,13 +7088,13 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B351" t="n">
-        <v>0.3653474903474903</v>
+        <v>0.3552123552123552</v>
       </c>
       <c r="C351" t="n">
-        <v>759</v>
+        <v>738</v>
       </c>
       <c r="D351" t="n">
         <v>2</v>
@@ -7107,16 +7107,16 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B352" t="n">
-        <v>0.3638996138996138</v>
+        <v>0.3547297297297297</v>
       </c>
       <c r="C352" t="n">
-        <v>757</v>
+        <v>736</v>
       </c>
       <c r="D352" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -7126,13 +7126,13 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B353" t="n">
-        <v>0.3629343629343629</v>
+        <v>0.3537644787644787</v>
       </c>
       <c r="C353" t="n">
-        <v>754</v>
+        <v>735</v>
       </c>
       <c r="D353" t="n">
         <v>2</v>
@@ -7145,16 +7145,16 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B354" t="n">
-        <v>0.3624517374517374</v>
+        <v>0.3527992277992277</v>
       </c>
       <c r="C354" t="n">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -7164,16 +7164,16 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B355" t="n">
-        <v>0.3610038610038609</v>
+        <v>0.3518339768339768</v>
       </c>
       <c r="C355" t="n">
-        <v>751</v>
+        <v>731</v>
       </c>
       <c r="D355" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -7183,13 +7183,13 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B356" t="n">
-        <v>0.3605212355212354</v>
+        <v>0.3513513513513513</v>
       </c>
       <c r="C356" t="n">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="D356" t="n">
         <v>1</v>
@@ -7202,16 +7202,16 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B357" t="n">
-        <v>0.3595559845559845</v>
+        <v>0.3499034749034749</v>
       </c>
       <c r="C357" t="n">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="D357" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -7221,16 +7221,16 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B358" t="n">
-        <v>0.359073359073359</v>
+        <v>0.3484555984555984</v>
       </c>
       <c r="C358" t="n">
-        <v>745</v>
+        <v>725</v>
       </c>
       <c r="D358" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -7240,16 +7240,16 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B359" t="n">
-        <v>0.3576254826254825</v>
+        <v>0.3474903474903475</v>
       </c>
       <c r="C359" t="n">
-        <v>744</v>
+        <v>722</v>
       </c>
       <c r="D359" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -7259,13 +7259,13 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B360" t="n">
-        <v>0.3566602316602316</v>
+        <v>0.3465250965250965</v>
       </c>
       <c r="C360" t="n">
-        <v>741</v>
+        <v>720</v>
       </c>
       <c r="D360" t="n">
         <v>2</v>
@@ -7278,16 +7278,16 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B361" t="n">
-        <v>0.3556949806949806</v>
+        <v>0.346042471042471</v>
       </c>
       <c r="C361" t="n">
-        <v>739</v>
+        <v>718</v>
       </c>
       <c r="D361" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -7297,16 +7297,16 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B362" t="n">
-        <v>0.3532818532818532</v>
+        <v>0.3455598455598456</v>
       </c>
       <c r="C362" t="n">
-        <v>737</v>
+        <v>717</v>
       </c>
       <c r="D362" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -7316,16 +7316,16 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B363" t="n">
-        <v>0.3523166023166023</v>
+        <v>0.3450772200772201</v>
       </c>
       <c r="C363" t="n">
-        <v>732</v>
+        <v>716</v>
       </c>
       <c r="D363" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -7335,16 +7335,16 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B364" t="n">
-        <v>0.3518339768339768</v>
+        <v>0.3436293436293436</v>
       </c>
       <c r="C364" t="n">
-        <v>730</v>
+        <v>715</v>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -7354,16 +7354,16 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B365" t="n">
-        <v>0.3513513513513513</v>
+        <v>0.3426640926640926</v>
       </c>
       <c r="C365" t="n">
-        <v>729</v>
+        <v>712</v>
       </c>
       <c r="D365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -7373,16 +7373,16 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B366" t="n">
-        <v>0.3503861003861004</v>
+        <v>0.3421814671814671</v>
       </c>
       <c r="C366" t="n">
-        <v>728</v>
+        <v>710</v>
       </c>
       <c r="D366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -7392,13 +7392,13 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B367" t="n">
-        <v>0.3494208494208494</v>
+        <v>0.3412162162162162</v>
       </c>
       <c r="C367" t="n">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="D367" t="n">
         <v>2</v>
@@ -7411,16 +7411,16 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B368" t="n">
-        <v>0.3489382239382239</v>
+        <v>0.3402509652509652</v>
       </c>
       <c r="C368" t="n">
-        <v>724</v>
+        <v>707</v>
       </c>
       <c r="D368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -7430,13 +7430,13 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B369" t="n">
-        <v>0.347972972972973</v>
+        <v>0.3392857142857142</v>
       </c>
       <c r="C369" t="n">
-        <v>723</v>
+        <v>705</v>
       </c>
       <c r="D369" t="n">
         <v>2</v>
@@ -7449,16 +7449,16 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B370" t="n">
-        <v>0.3474903474903475</v>
+        <v>0.3373552123552123</v>
       </c>
       <c r="C370" t="n">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="D370" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -7468,37 +7468,18 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B371" t="n">
-        <v>0.3455598455598455</v>
+        <v>0.3368725868725869</v>
       </c>
       <c r="C371" t="n">
-        <v>720</v>
+        <v>699</v>
       </c>
       <c r="D371" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E371" t="inlineStr">
-        <is>
-          <t>High predicted risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="n">
-        <v>180</v>
-      </c>
-      <c r="B372" t="n">
-        <v>0.34507722007722</v>
-      </c>
-      <c r="C372" t="n">
-        <v>716</v>
-      </c>
-      <c r="D372" t="n">
-        <v>1</v>
-      </c>
-      <c r="E372" t="inlineStr">
         <is>
           <t>High predicted risk</t>
         </is>
